--- a/ig/TEST-SUPPLEMENT/CodeSystem-specimenType-supplement-fr.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-specimenType-supplement-fr.xlsx
@@ -72,7 +72,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Traduction Francaise</t>
+    <t>Traduction Française</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/TEST-SUPPLEMENT/CodeSystem-specimenType-supplement-fr.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-specimenType-supplement-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="350">
   <si>
     <t>Property</t>
   </si>
@@ -192,9 +192,6 @@
     <t>BLDA</t>
   </si>
   <si>
-    <t>BLDC</t>
-  </si>
-  <si>
     <t>BLDCO</t>
   </si>
   <si>
@@ -225,9 +222,6 @@
     <t>BRN</t>
   </si>
   <si>
-    <t>BRO</t>
-  </si>
-  <si>
     <t>BRSH</t>
   </si>
   <si>
@@ -276,9 +270,6 @@
     <t>CONE</t>
   </si>
   <si>
-    <t>CRN</t>
-  </si>
-  <si>
     <t>CSCR</t>
   </si>
   <si>
@@ -315,9 +306,6 @@
     <t>CVPT</t>
   </si>
   <si>
-    <t>CVX</t>
-  </si>
-  <si>
     <t>CYN</t>
   </si>
   <si>
@@ -348,9 +336,6 @@
     <t>DIV</t>
   </si>
   <si>
-    <t>DOSE</t>
-  </si>
-  <si>
     <t>DRN</t>
   </si>
   <si>
@@ -363,9 +348,6 @@
     <t>DUFL</t>
   </si>
   <si>
-    <t>EAR</t>
-  </si>
-  <si>
     <t>EARW</t>
   </si>
   <si>
@@ -390,12 +372,6 @@
     <t>ELT</t>
   </si>
   <si>
-    <t>ENDC</t>
-  </si>
-  <si>
-    <t>ENDM</t>
-  </si>
-  <si>
     <t>ENVIR</t>
   </si>
   <si>
@@ -432,9 +408,6 @@
     <t>EXUDTE</t>
   </si>
   <si>
-    <t>EYE</t>
-  </si>
-  <si>
     <t>FAW</t>
   </si>
   <si>
@@ -465,9 +438,6 @@
     <t>FOLEY</t>
   </si>
   <si>
-    <t>FOOD</t>
-  </si>
-  <si>
     <t>FRS</t>
   </si>
   <si>
@@ -495,15 +465,6 @@
     <t>GAST</t>
   </si>
   <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>GENC</t>
-  </si>
-  <si>
-    <t>GENF</t>
-  </si>
-  <si>
     <t>GENL</t>
   </si>
   <si>
@@ -627,9 +588,6 @@
     <t>KIDFLD</t>
   </si>
   <si>
-    <t>LAM</t>
-  </si>
-  <si>
     <t>LAVG</t>
   </si>
   <si>
@@ -657,9 +615,6 @@
     <t>LIQO</t>
   </si>
   <si>
-    <t>LN</t>
-  </si>
-  <si>
     <t>LNA</t>
   </si>
   <si>
@@ -726,9 +681,6 @@
     <t>NODUL</t>
   </si>
   <si>
-    <t>NOS</t>
-  </si>
-  <si>
     <t>NSECR</t>
   </si>
   <si>
@@ -747,9 +699,6 @@
     <t>PAFL</t>
   </si>
   <si>
-    <t>PAT</t>
-  </si>
-  <si>
     <t>PCFL</t>
   </si>
   <si>
@@ -825,9 +774,6 @@
     <t>PRP</t>
   </si>
   <si>
-    <t>PRT</t>
-  </si>
-  <si>
     <t>PSC</t>
   </si>
   <si>
@@ -903,9 +849,6 @@
     <t>SKBP</t>
   </si>
   <si>
-    <t>SKM</t>
-  </si>
-  <si>
     <t>SKN</t>
   </si>
   <si>
@@ -915,9 +858,6 @@
     <t>SMN</t>
   </si>
   <si>
-    <t>SMPLS</t>
-  </si>
-  <si>
     <t>SNV</t>
   </si>
   <si>
@@ -990,15 +930,6 @@
     <t>THRB</t>
   </si>
   <si>
-    <t>THRT</t>
-  </si>
-  <si>
-    <t>TISG</t>
-  </si>
-  <si>
-    <t>TISPL</t>
-  </si>
-  <si>
     <t>TISS</t>
   </si>
   <si>
@@ -1008,12 +939,6 @@
     <t>TLC</t>
   </si>
   <si>
-    <t>TLGI</t>
-  </si>
-  <si>
-    <t>TLNG</t>
-  </si>
-  <si>
     <t>TRAC</t>
   </si>
   <si>
@@ -1023,18 +948,12 @@
     <t>TSERU</t>
   </si>
   <si>
-    <t>TSMI</t>
-  </si>
-  <si>
     <t>TSTES</t>
   </si>
   <si>
     <t>TTRA</t>
   </si>
   <si>
-    <t>TUB</t>
-  </si>
-  <si>
     <t>TUBES</t>
   </si>
   <si>
@@ -1047,12 +966,6 @@
     <t>UDENT</t>
   </si>
   <si>
-    <t>ULC</t>
-  </si>
-  <si>
-    <t>UMB</t>
-  </si>
-  <si>
     <t>UMED</t>
   </si>
   <si>
@@ -1081,9 +994,6 @@
   </si>
   <si>
     <t>URT</t>
-  </si>
-  <si>
-    <t>URTH</t>
   </si>
   <si>
     <t>USCOP</t>
@@ -1450,7 +1360,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D344"/>
+  <dimension ref="A1:D314"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4597,306 +4507,6 @@
       <c r="C314" s="2"/>
       <c r="D314" s="2"/>
     </row>
-    <row r="315">
-      <c r="A315" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B315" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C315" s="2"/>
-      <c r="D315" s="2"/>
-    </row>
-    <row r="316">
-      <c r="A316" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B316" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C316" s="2"/>
-      <c r="D316" s="2"/>
-    </row>
-    <row r="317">
-      <c r="A317" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B317" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C317" s="2"/>
-      <c r="D317" s="2"/>
-    </row>
-    <row r="318">
-      <c r="A318" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B318" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C318" s="2"/>
-      <c r="D318" s="2"/>
-    </row>
-    <row r="319">
-      <c r="A319" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B319" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C319" s="2"/>
-      <c r="D319" s="2"/>
-    </row>
-    <row r="320">
-      <c r="A320" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B320" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C320" s="2"/>
-      <c r="D320" s="2"/>
-    </row>
-    <row r="321">
-      <c r="A321" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B321" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C321" s="2"/>
-      <c r="D321" s="2"/>
-    </row>
-    <row r="322">
-      <c r="A322" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B322" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C322" s="2"/>
-      <c r="D322" s="2"/>
-    </row>
-    <row r="323">
-      <c r="A323" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B323" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C323" s="2"/>
-      <c r="D323" s="2"/>
-    </row>
-    <row r="324">
-      <c r="A324" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B324" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C324" s="2"/>
-      <c r="D324" s="2"/>
-    </row>
-    <row r="325">
-      <c r="A325" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B325" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C325" s="2"/>
-      <c r="D325" s="2"/>
-    </row>
-    <row r="326">
-      <c r="A326" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B326" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C326" s="2"/>
-      <c r="D326" s="2"/>
-    </row>
-    <row r="327">
-      <c r="A327" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B327" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C327" s="2"/>
-      <c r="D327" s="2"/>
-    </row>
-    <row r="328">
-      <c r="A328" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B328" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C328" s="2"/>
-      <c r="D328" s="2"/>
-    </row>
-    <row r="329">
-      <c r="A329" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B329" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C329" s="2"/>
-      <c r="D329" s="2"/>
-    </row>
-    <row r="330">
-      <c r="A330" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B330" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C330" s="2"/>
-      <c r="D330" s="2"/>
-    </row>
-    <row r="331">
-      <c r="A331" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B331" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C331" s="2"/>
-      <c r="D331" s="2"/>
-    </row>
-    <row r="332">
-      <c r="A332" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B332" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C332" s="2"/>
-      <c r="D332" s="2"/>
-    </row>
-    <row r="333">
-      <c r="A333" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B333" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C333" s="2"/>
-      <c r="D333" s="2"/>
-    </row>
-    <row r="334">
-      <c r="A334" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B334" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C334" s="2"/>
-      <c r="D334" s="2"/>
-    </row>
-    <row r="335">
-      <c r="A335" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B335" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C335" s="2"/>
-      <c r="D335" s="2"/>
-    </row>
-    <row r="336">
-      <c r="A336" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B336" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C336" s="2"/>
-      <c r="D336" s="2"/>
-    </row>
-    <row r="337">
-      <c r="A337" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B337" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C337" s="2"/>
-      <c r="D337" s="2"/>
-    </row>
-    <row r="338">
-      <c r="A338" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B338" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C338" s="2"/>
-      <c r="D338" s="2"/>
-    </row>
-    <row r="339">
-      <c r="A339" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B339" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C339" s="2"/>
-      <c r="D339" s="2"/>
-    </row>
-    <row r="340">
-      <c r="A340" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B340" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C340" s="2"/>
-      <c r="D340" s="2"/>
-    </row>
-    <row r="341">
-      <c r="A341" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B341" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C341" s="2"/>
-      <c r="D341" s="2"/>
-    </row>
-    <row r="342">
-      <c r="A342" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B342" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C342" s="2"/>
-      <c r="D342" s="2"/>
-    </row>
-    <row r="343">
-      <c r="A343" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B343" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C343" s="2"/>
-      <c r="D343" s="2"/>
-    </row>
-    <row r="344">
-      <c r="A344" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B344" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C344" s="2"/>
-      <c r="D344" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
